--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1213E58A-A316-4B5C-922E-0568B4EFADE9}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61C5D86F-BBFB-4E41-8A0B-6D7AA3C4B463}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11895" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -137,127 +137,118 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>31 ago</t>
-  </si>
-  <si>
-    <t>1 sept</t>
-  </si>
-  <si>
-    <t>2 sept</t>
-  </si>
-  <si>
-    <t>3 sept</t>
-  </si>
-  <si>
-    <t>4 sept</t>
-  </si>
-  <si>
-    <t>5 sept</t>
-  </si>
-  <si>
-    <t>6 sept</t>
-  </si>
-  <si>
-    <t>Sopa de mazorca</t>
-  </si>
-  <si>
-    <t>Carne a la cerveza</t>
-  </si>
-  <si>
-    <t>Cascos de papa dorada</t>
-  </si>
-  <si>
-    <t>Ensalada del sol</t>
-  </si>
-  <si>
-    <t>Arroz al cebollín</t>
-  </si>
-  <si>
     <t>Sopa de pasta</t>
   </si>
   <si>
-    <t>Arroz con pollo</t>
-  </si>
-  <si>
-    <t>Plátano al horno con queso y bocadillo</t>
-  </si>
-  <si>
-    <t>Ensalada al huevo</t>
-  </si>
-  <si>
-    <t>Bandeja paisa</t>
-  </si>
-  <si>
-    <t>9 acompañamientos</t>
-  </si>
-  <si>
-    <t>Sopa de arracacha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carne molina, chicharrón, chorizo, fríjoles, huevo, plátano, aguacate, arepa y arroz blanco </t>
-  </si>
-  <si>
     <t>Monedas de plátano con queso</t>
   </si>
   <si>
-    <t>Ensalada bellavista</t>
-  </si>
-  <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
-    <t>Pechuga rellena</t>
-  </si>
-  <si>
-    <t>Con jamón y queso</t>
-  </si>
-  <si>
-    <t>Papa duquesa</t>
-  </si>
-  <si>
-    <t>Ensalada mil islas</t>
-  </si>
-  <si>
-    <t>Arroz malteado</t>
-  </si>
-  <si>
-    <t>Sopa de colicero</t>
-  </si>
-  <si>
-    <t>Filete de mojarra</t>
-  </si>
-  <si>
-    <t>En salsa de camarones</t>
-  </si>
-  <si>
-    <t>Enyucado</t>
-  </si>
-  <si>
-    <t>Arroz palito</t>
-  </si>
-  <si>
-    <t>Yuca dorada</t>
-  </si>
-  <si>
-    <t>Sidra en salsa al pimentón</t>
-  </si>
-  <si>
-    <t>Crema de zuchinni</t>
-  </si>
-  <si>
-    <t>Pollo oriental</t>
-  </si>
-  <si>
-    <t>En salsa de mango</t>
-  </si>
-  <si>
-    <t>Copos de papa con ajonjolí</t>
-  </si>
-  <si>
-    <t>Ensalada mediterránea</t>
+    <t>7 sept</t>
+  </si>
+  <si>
+    <t>8 sept</t>
+  </si>
+  <si>
+    <t>9 sept</t>
+  </si>
+  <si>
+    <t>10 sept</t>
+  </si>
+  <si>
+    <t>11 sept</t>
+  </si>
+  <si>
+    <t>12 sept</t>
+  </si>
+  <si>
+    <t>13 sept</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco trigo</t>
+  </si>
+  <si>
+    <t>Costillas de cerdo a la BBQ</t>
+  </si>
+  <si>
+    <t>Papa asada</t>
+  </si>
+  <si>
+    <t>Verduras salteadas</t>
+  </si>
+  <si>
+    <t>Sopa de verduras</t>
+  </si>
+  <si>
+    <t>Pollo a la cazadora</t>
+  </si>
+  <si>
+    <t>Anillos de cebolla a la orly</t>
+  </si>
+  <si>
+    <t>Ensalada primavera</t>
+  </si>
+  <si>
+    <t>Arroz con hilos de espinaca</t>
+  </si>
+  <si>
+    <t>Sopa de patación</t>
+  </si>
+  <si>
+    <t>Hígado a la plancha</t>
+  </si>
+  <si>
+    <t>Yuca a la criolla</t>
+  </si>
+  <si>
+    <t>Ensalada fantasía</t>
+  </si>
+  <si>
+    <t>Arroz al pimentón</t>
+  </si>
+  <si>
+    <t>Pollo a la vizcaína</t>
+  </si>
+  <si>
+    <t>Papa hashbrown</t>
+  </si>
+  <si>
+    <t>Ensalada al pesto</t>
+  </si>
+  <si>
+    <t>Arroz al perejil</t>
+  </si>
+  <si>
+    <t>Crema de ahuyama</t>
+  </si>
+  <si>
+    <t>Rollo de carne</t>
+  </si>
+  <si>
+    <t>En salsa strogonoff</t>
+  </si>
+  <si>
+    <t>Papa al perejil</t>
+  </si>
+  <si>
+    <t>Ensalada de verano</t>
+  </si>
+  <si>
+    <t>Guacamole</t>
+  </si>
+  <si>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>Costilla de res</t>
+  </si>
+  <si>
+    <t>Yuca - Mazorca - Plátano</t>
+  </si>
+  <si>
+    <t>Sopa de maíz pintado</t>
+  </si>
+  <si>
+    <t>Yuca o plátano</t>
   </si>
 </sst>
 </file>
@@ -319,7 +310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -342,11 +333,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE4D6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE4D6C6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -371,6 +373,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -713,14 +718,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -729,14 +734,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -745,14 +750,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -761,14 +766,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -777,14 +782,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -793,13 +798,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="4"/>
@@ -809,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -825,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
@@ -841,7 +846,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
@@ -857,13 +862,15 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -871,53 +878,47 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -925,15 +926,15 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -941,270 +942,268 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E29" s="4" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E30" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E31" s="4" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1213,19 +1212,19 @@
         <v>13</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1233,16 +1232,16 @@
         <v>13</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1251,16 +1250,16 @@
         <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F34" s="4"/>
     </row>
@@ -1269,13 +1268,13 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>7</v>
@@ -1284,90 +1283,88 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>7</v>
@@ -1379,33 +1376,36 @@
         <v>23</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4" t="s">
+      <c r="D41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E42" s="4" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -1413,74 +1413,62 @@
         <v>23</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="4"/>
+      <c r="D43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F44" s="4"/>
+      <c r="D44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B46" s="8"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="8"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B48" s="8"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B49" s="8"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B50" s="8"/>
+      <c r="D45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2529D65A-E14F-4754-86E2-EC26A04AA7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="77">
   <si>
     <t>Menú de Santa Ana 109 — Golconda</t>
   </si>
@@ -34,169 +34,169 @@
     <t>Día</t>
   </si>
   <si>
+    <t>IMPORTANTE: este archivo es SOLO del punto Santa Ana 109. El otro punto tiene su propio archivo.</t>
+  </si>
+  <si>
+    <t>1) Cada FILA es un plato. Un plato por fila.</t>
+  </si>
+  <si>
+    <t>2) «Día»: elígelo en la lista desplegable.</t>
+  </si>
+  <si>
+    <t>3) «Fecha»: la que se muestra (ej. 13 jul). Repítela en todas las filas de ese día.</t>
+  </si>
+  <si>
+    <t>4) «Festivo»: «Sí» solo si ese día cobra tarifa de domingo/festivo; si no, «No».</t>
+  </si>
+  <si>
+    <t>5) «Plato»: el nombre del plato.</t>
+  </si>
+  <si>
+    <t>6) «Descripción»: nota corta que aparece DEBAJO del plato (opcional).</t>
+  </si>
+  <si>
     <t>Fecha</t>
   </si>
   <si>
     <t>Festivo</t>
   </si>
   <si>
-    <t>IMPORTANTE: este archivo es SOLO del punto Santa Ana 109. El otro punto tiene su propio archivo.</t>
+    <t>Días con dos menús (como el sábado)</t>
   </si>
   <si>
     <t>Opción</t>
   </si>
   <si>
+    <t>• Llena «Opción» con «Opción 1» y «Opción 2». Si hay un solo menú, déjala vacía.</t>
+  </si>
+  <si>
     <t>Plato</t>
   </si>
   <si>
     <t>Descripción</t>
   </si>
   <si>
-    <t>1) Cada FILA es un plato. Un plato por fila.</t>
-  </si>
-  <si>
-    <t>2) «Día»: elígelo en la lista desplegable.</t>
-  </si>
-  <si>
-    <t>3) «Fecha»: la que se muestra (ej. 13 jul). Repítela en todas las filas de ese día.</t>
-  </si>
-  <si>
-    <t>4) «Festivo»: «Sí» solo si ese día cobra tarifa de domingo/festivo; si no, «No».</t>
-  </si>
-  <si>
-    <t>5) «Plato»: el nombre del plato.</t>
-  </si>
-  <si>
-    <t>6) «Descripción»: nota corta que aparece DEBAJO del plato (opcional).</t>
+    <t>Publicar</t>
+  </si>
+  <si>
+    <t>Guarda con el nombre menu-santaana.xlsx y súbelo a GitHub reemplazando el anterior.</t>
+  </si>
+  <si>
+    <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
     <t>Lunes</t>
   </si>
   <si>
-    <t>Días con dos menús (como el sábado)</t>
-  </si>
-  <si>
-    <t>• Llena «Opción» con «Opción 1» y «Opción 2». Si hay un solo menú, déjala vacía.</t>
-  </si>
-  <si>
-    <t>14 sept</t>
-  </si>
-  <si>
-    <t>Publicar</t>
-  </si>
-  <si>
-    <t>Guarda con el nombre menu-santaana.xlsx y súbelo a GitHub reemplazando el anterior.</t>
-  </si>
-  <si>
-    <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
+    <t>21 sept</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Sopa de sancocho</t>
-  </si>
-  <si>
-    <t>Bistec a caballo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bananitos al horno </t>
-  </si>
-  <si>
-    <t>En salsa de naranja</t>
-  </si>
-  <si>
-    <t>Ensalada frita de garbanzos</t>
+    <t>Sopa de mazorca</t>
+  </si>
+  <si>
+    <t>Carne desmechada</t>
+  </si>
+  <si>
+    <t>Patacón</t>
+  </si>
+  <si>
+    <t>Ensalada primavera</t>
+  </si>
+  <si>
+    <t>Arroz con caraota</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>22 sept</t>
+  </si>
+  <si>
+    <t>Sopa de avena</t>
+  </si>
+  <si>
+    <t>Alitas de pollo a la broaster</t>
+  </si>
+  <si>
+    <t>Papa alemana</t>
+  </si>
+  <si>
+    <t>Ensalada de pepino cohombro</t>
+  </si>
+  <si>
+    <t>Con yogurt</t>
+  </si>
+  <si>
+    <t>Arroz con arveja</t>
+  </si>
+  <si>
+    <t>Miércoles</t>
+  </si>
+  <si>
+    <t>23 sept</t>
+  </si>
+  <si>
+    <t>Sopa madrileña</t>
+  </si>
+  <si>
+    <t>Lengua napolitana</t>
+  </si>
+  <si>
+    <t>Puré de papa mixto</t>
+  </si>
+  <si>
+    <t>Ensalada veraniega</t>
   </si>
   <si>
     <t>Arroz blanco</t>
   </si>
   <si>
-    <t>Martes</t>
-  </si>
-  <si>
-    <t>15 sept</t>
-  </si>
-  <si>
-    <t>Sopa de Minestrone</t>
-  </si>
-  <si>
-    <t>Papa a la francesa</t>
-  </si>
-  <si>
-    <t>Ensalada mil islas</t>
-  </si>
-  <si>
-    <t>Arroz malteado</t>
-  </si>
-  <si>
-    <t>Miércoles</t>
-  </si>
-  <si>
-    <t>16 sept</t>
-  </si>
-  <si>
-    <t>Arroz mixto</t>
-  </si>
-  <si>
-    <t>Pollo, res y cerdo</t>
-  </si>
-  <si>
-    <t>Chop suey</t>
-  </si>
-  <si>
-    <t>Rollitos de piña</t>
-  </si>
-  <si>
-    <t>En salsa agridulce</t>
-  </si>
-  <si>
     <t>Jueves</t>
   </si>
   <si>
-    <t>17 sept</t>
-  </si>
-  <si>
-    <t>Sopa de cebada perlada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pollo gratinado </t>
-  </si>
-  <si>
-    <t>En salsa de ciruelas</t>
-  </si>
-  <si>
-    <t>Cascos de papa</t>
-  </si>
-  <si>
-    <t>Ensalada cesar</t>
-  </si>
-  <si>
-    <t>Arroz verde</t>
+    <t>24 sept</t>
+  </si>
+  <si>
+    <t>Sopa de arroz con menudencias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spaguettis mixtos </t>
+  </si>
+  <si>
+    <t>Ensalada de otoño</t>
+  </si>
+  <si>
+    <t>Papa crisper</t>
   </si>
   <si>
     <t>Viernes</t>
   </si>
   <si>
-    <t>18 sept</t>
-  </si>
-  <si>
-    <t>Sopa de tortilla de huevo</t>
-  </si>
-  <si>
-    <t>Arracacha chip</t>
-  </si>
-  <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>Arroz pajarito</t>
+    <t>25 sept</t>
+  </si>
+  <si>
+    <t>Sopa de pasta</t>
+  </si>
+  <si>
+    <t>Pollo tropical</t>
+  </si>
+  <si>
+    <t>Dedito de queso mozarella</t>
+  </si>
+  <si>
+    <t>Ensalada tropical</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
   </si>
   <si>
     <t>Sábado</t>
   </si>
   <si>
-    <t>19 sept</t>
+    <t>26 sept</t>
   </si>
   <si>
     <t>Opción 1</t>
@@ -226,46 +226,37 @@
     <t>Elige tu proteína</t>
   </si>
   <si>
-    <t>Papa criolla dorada</t>
-  </si>
-  <si>
-    <t>Pepinos a la criolla</t>
+    <t>Mini croquetas de yuca</t>
+  </si>
+  <si>
+    <t>Zanahoria vicky</t>
   </si>
   <si>
     <t>Domingo</t>
   </si>
   <si>
-    <t>20 sept</t>
+    <t>27 sept</t>
   </si>
   <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>Sopa de patacón</t>
-  </si>
-  <si>
-    <t>Papa a la griega</t>
-  </si>
-  <si>
-    <t>Ensalada cherry</t>
-  </si>
-  <si>
-    <t>Fricasé de pollo y champiñones</t>
-  </si>
-  <si>
-    <t>Crema de apio</t>
-  </si>
-  <si>
-    <t>En salsa tártara</t>
-  </si>
-  <si>
-    <t>Filete de tilapia crunch</t>
-  </si>
-  <si>
-    <t>Pierna pernil mediterránea</t>
-  </si>
-  <si>
-    <t>Arroz con quinoa</t>
+    <t>Sopa de mute</t>
+  </si>
+  <si>
+    <t>Churrasco a la plancha</t>
+  </si>
+  <si>
+    <t>Papa a la crema</t>
+  </si>
+  <si>
+    <t>Ensalada roja</t>
+  </si>
+  <si>
+    <t>Con pollo y bolognesa</t>
+  </si>
+  <si>
+    <t>Pan francés con ajo</t>
   </si>
 </sst>
 </file>
@@ -286,12 +277,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
@@ -300,6 +285,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF4A3524"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -366,28 +357,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -606,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F999"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -618,31 +609,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>7</v>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>21</v>
@@ -655,10 +646,10 @@
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>21</v>
@@ -671,10 +662,10 @@
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>21</v>
@@ -683,80 +674,78 @@
       <c r="E4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>21</v>
@@ -769,10 +758,10 @@
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>21</v>
@@ -781,114 +770,112 @@
       <c r="E10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="8" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>37</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="8" t="s">
         <v>40</v>
       </c>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>21</v>
@@ -897,159 +884,153 @@
       <c r="E17" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="8"/>
+        <v>45</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>76</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>59</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
@@ -1065,9 +1046,11 @@
         <v>57</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
@@ -1083,7 +1066,7 @@
         <v>57</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" s="8"/>
     </row>
@@ -1101,7 +1084,7 @@
         <v>57</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F29" s="8"/>
     </row>
@@ -1116,10 +1099,10 @@
         <v>21</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="F30" s="8"/>
     </row>
@@ -1137,11 +1120,9 @@
         <v>62</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>65</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
@@ -1157,9 +1138,11 @@
         <v>62</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
@@ -1175,7 +1158,7 @@
         <v>62</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" s="8"/>
     </row>
@@ -1193,23 +1176,25 @@
         <v>62</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E35" s="8" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F35" s="8"/>
     </row>
@@ -1225,7 +1210,7 @@
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F36" s="8"/>
     </row>
@@ -1273,31 +1258,40 @@
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
+      <c r="A40" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="D40" s="7"/>
-      <c r="E40" s="9"/>
+      <c r="E40" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="6"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="9"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
@@ -1314,9 +1308,11 @@
       <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="9"/>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
@@ -3088,7 +3084,11 @@
       <c r="C399" s="10"/>
       <c r="D399" s="10"/>
     </row>
-    <row r="400" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A400" s="10"/>
+      <c r="C400" s="10"/>
+      <c r="D400" s="10"/>
+    </row>
     <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -3688,15 +3688,16 @@
     <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D399" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C399" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="A2:A399" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3720,75 +3721,75 @@
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-    </row>
-    <row r="5" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="7" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+    <row r="11" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+    <row r="13" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="14" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+    <row r="16" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83CAC428-0B9B-417E-A852-5C2EF45F6CBB}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18CDAC0B-37E9-4550-B7E3-779BED706848}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="78">
   <si>
     <t>Menú de Santa Ana 109 — Golconda</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Martes</t>
   </si>
   <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
     <t>Miércoles</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>Sopa de ajiaco</t>
   </si>
   <si>
-    <t>Carne de res / Pollo / Chuleta de cerdo</t>
-  </si>
-  <si>
     <t>Elige tu proteína</t>
   </si>
   <si>
@@ -145,122 +139,134 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>28 sept</t>
-  </si>
-  <si>
-    <t>29 sept</t>
-  </si>
-  <si>
-    <t>30 sept</t>
-  </si>
-  <si>
-    <t>1 oct</t>
-  </si>
-  <si>
-    <t>2 oct</t>
-  </si>
-  <si>
-    <t>3 oct</t>
-  </si>
-  <si>
-    <t>4 oct</t>
-  </si>
-  <si>
-    <t>Sopa de cascabeles</t>
-  </si>
-  <si>
-    <t>Carne a las finas hierbas</t>
-  </si>
-  <si>
-    <t>Soufflé de papa</t>
-  </si>
-  <si>
-    <t>Ensalada mediterránea</t>
-  </si>
-  <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Sopa de torrejas</t>
-  </si>
-  <si>
-    <t>Pollo al horno</t>
-  </si>
-  <si>
-    <t>Papa salada</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
-    <t>Arroz con verduras</t>
-  </si>
-  <si>
-    <t>Sopa de arracacha</t>
-  </si>
-  <si>
-    <t>Chuleta de cerdo a la plancha</t>
-  </si>
-  <si>
-    <t>Croqueta de yuca</t>
-  </si>
-  <si>
-    <t>Ensalada oriental</t>
-  </si>
-  <si>
-    <t>Arroz con cabello de ángel</t>
-  </si>
-  <si>
-    <t>Sopa de verduras</t>
-  </si>
-  <si>
-    <t>Pollo maryland</t>
-  </si>
-  <si>
-    <t>Papa hash brown</t>
-  </si>
-  <si>
-    <t>Ensalada de zuchinni</t>
-  </si>
-  <si>
-    <t>Sopa de sancocho de pescado</t>
-  </si>
-  <si>
-    <t>Filete de mojarra a la plancha</t>
-  </si>
-  <si>
-    <t>Patacón con hogao</t>
-  </si>
-  <si>
-    <t>Ensalada con aguacate</t>
-  </si>
-  <si>
-    <t>Arroz con coco</t>
-  </si>
-  <si>
-    <t>Torta de banano</t>
-  </si>
-  <si>
-    <t>Habichuelas a la criolla</t>
-  </si>
-  <si>
-    <t>Milanesa de pollo</t>
-  </si>
-  <si>
-    <t>Con ajonjolí</t>
-  </si>
-  <si>
-    <t>Papa al perejil</t>
-  </si>
-  <si>
-    <t>Verduras al gratín</t>
+    <t>5 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de maíz</t>
+  </si>
+  <si>
+    <t>Carne encebollada</t>
+  </si>
+  <si>
+    <t>Platano al horno con queso y bocadillo</t>
+  </si>
+  <si>
+    <t>Ensalada campesina</t>
+  </si>
+  <si>
+    <t>Arroz al pimentón</t>
+  </si>
+  <si>
+    <t>6 oct</t>
+  </si>
+  <si>
+    <t>Sopa de colicero</t>
+  </si>
+  <si>
+    <t>Pollo a la broaster</t>
+  </si>
+  <si>
+    <t>Papa postiza</t>
+  </si>
+  <si>
+    <t>Ensalada hawaiana</t>
+  </si>
+  <si>
+    <t>Arroz verde</t>
+  </si>
+  <si>
+    <t>7 oct</t>
+  </si>
+  <si>
+    <t>Bandeja paisa</t>
+  </si>
+  <si>
+    <t>9 acompañamientos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carne molina, chicharrón, chorizo, fríjoles, huevo, plátano, aguacate, arepa y arroz blanco </t>
+  </si>
+  <si>
+    <t>Sopa de maíz pintado</t>
+  </si>
+  <si>
+    <t>Carne de res / pollo / chuleta de cerdo</t>
+  </si>
+  <si>
+    <t>Monedas de plátano con queso</t>
+  </si>
+  <si>
+    <t>Ensalada mixta a la vinagreta</t>
+  </si>
+  <si>
+    <t>8 oct</t>
+  </si>
+  <si>
+    <t>Sopa de Minestrone</t>
+  </si>
+  <si>
+    <t>Pechuga rellena con queso y espinaca</t>
+  </si>
+  <si>
+    <t>En salsa miel mostaza</t>
+  </si>
+  <si>
+    <t>Copitos de papa al cebollín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensalada de pepino cohombro </t>
+  </si>
+  <si>
+    <t>Con yogurt</t>
+  </si>
+  <si>
+    <t>9 oct</t>
+  </si>
+  <si>
+    <t>Crema de apío</t>
+  </si>
+  <si>
+    <t>Pollo a la naranja</t>
+  </si>
+  <si>
+    <t>Papa smile</t>
+  </si>
+  <si>
+    <t>Soufflé de berenjena</t>
+  </si>
+  <si>
+    <t>Arroz con ajonjolí</t>
+  </si>
+  <si>
+    <t>10 oct</t>
+  </si>
+  <si>
+    <t>Yuca a la criolla</t>
+  </si>
+  <si>
+    <t>Ensalada fantasía</t>
+  </si>
+  <si>
+    <t>11 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de trigo</t>
+  </si>
+  <si>
+    <t>Pollo al BBQ</t>
+  </si>
+  <si>
+    <t>Papa asada</t>
+  </si>
+  <si>
+    <t>Verduras salteadas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,6 +301,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -379,7 +391,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -397,6 +409,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,14 +649,14 @@
         <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F2" s="8"/>
     </row>
@@ -649,14 +665,14 @@
         <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F3" s="8"/>
     </row>
@@ -665,14 +681,14 @@
         <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F4" s="8"/>
     </row>
@@ -681,14 +697,14 @@
         <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F5" s="8"/>
     </row>
@@ -697,14 +713,14 @@
         <v>19</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -713,14 +729,14 @@
         <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F7" s="8"/>
     </row>
@@ -729,14 +745,14 @@
         <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F8" s="8"/>
     </row>
@@ -745,14 +761,14 @@
         <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F9" s="8"/>
     </row>
@@ -761,14 +777,14 @@
         <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F10" s="8"/>
     </row>
@@ -777,540 +793,603 @@
         <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="E13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8" t="s">
-        <v>58</v>
-      </c>
+      <c r="D14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8" t="s">
-        <v>59</v>
-      </c>
+      <c r="D15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="8"/>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8" t="s">
-        <v>60</v>
-      </c>
+      <c r="D16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E17" s="8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="8"/>
+      <c r="D18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E19" s="8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E20" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E21" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="8" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D27" s="7"/>
       <c r="E27" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>30</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D28" s="7"/>
       <c r="E28" s="8" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D29" s="7"/>
       <c r="E29" s="8" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="D30" s="7"/>
       <c r="E30" s="8" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="D31" s="7"/>
       <c r="E31" s="8" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E36" s="8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E37" s="8" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E38" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E39" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E40" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
+      <c r="A41" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="9"/>
+      <c r="E41" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
+      <c r="A42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="F42" s="8"/>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
+      <c r="A43" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="D43" s="7"/>
-      <c r="E43" s="9"/>
+      <c r="E43" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
+      <c r="A44" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="D44" s="7"/>
-      <c r="E44" s="9"/>
+      <c r="E44" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
+      <c r="A45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="9"/>
+      <c r="E45" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10"/>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8B8A0F-1ABE-4DA2-A29F-21FEFDD5E96E}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBF05473-2F83-4388-8A24-8CFF0CEF224B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="75">
   <si>
     <t>Menú de Santa Ana 109 — Golconda</t>
   </si>
@@ -142,9 +142,6 @@
     <t>Ensalada romana</t>
   </si>
   <si>
-    <t>Arroz al perejíl</t>
-  </si>
-  <si>
     <t>19 oct</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>Torta de mazorca</t>
   </si>
   <si>
-    <t>Ensalada arco íris</t>
-  </si>
-  <si>
     <t>21 oct</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
     <t>Patacón</t>
   </si>
   <si>
-    <t xml:space="preserve">Arroz </t>
-  </si>
-  <si>
     <t>Sopa de durena</t>
   </si>
   <si>
@@ -250,10 +241,16 @@
     <t>Trucha al ajillo</t>
   </si>
   <si>
-    <t>Plátano chip</t>
-  </si>
-  <si>
     <t>Arroz con coco</t>
+  </si>
+  <si>
+    <t>Arroz Blanco</t>
+  </si>
+  <si>
+    <t>Platano chip</t>
+  </si>
+  <si>
+    <t>Ensalada arcoíris</t>
   </si>
 </sst>
 </file>
@@ -644,14 +641,14 @@
         <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -660,14 +657,14 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" s="9"/>
     </row>
@@ -676,14 +673,14 @@
         <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -692,14 +689,14 @@
         <v>19</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" s="9"/>
     </row>
@@ -708,14 +705,14 @@
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="F6" s="9"/>
     </row>
@@ -724,14 +721,14 @@
         <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -740,14 +737,14 @@
         <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="9"/>
     </row>
@@ -756,14 +753,14 @@
         <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="9"/>
     </row>
@@ -772,14 +769,14 @@
         <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F10" s="9"/>
     </row>
@@ -788,7 +785,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>20</v>
@@ -804,16 +801,16 @@
         <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -822,16 +819,16 @@
         <v>22</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -840,16 +837,16 @@
         <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -858,16 +855,16 @@
         <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -876,16 +873,16 @@
         <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -894,7 +891,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>20</v>
@@ -903,7 +900,7 @@
         <v>31</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F17" s="9"/>
     </row>
@@ -912,7 +909,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>20</v>
@@ -921,7 +918,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>33</v>
@@ -932,7 +929,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>20</v>
@@ -941,7 +938,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -950,7 +947,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>20</v>
@@ -959,25 +956,23 @@
         <v>31</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D21" s="8"/>
       <c r="E21" s="9" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F21" s="9"/>
     </row>
@@ -986,14 +981,14 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F22" s="9"/>
     </row>
@@ -1002,14 +997,14 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F23" s="9"/>
     </row>
@@ -1018,14 +1013,14 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F24" s="9"/>
     </row>
@@ -1034,30 +1029,30 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F26" s="9"/>
     </row>
@@ -1066,46 +1061,46 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F28" s="9"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F29" s="9"/>
     </row>
@@ -1114,30 +1109,30 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="9" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F31" s="9"/>
     </row>
@@ -1146,14 +1141,14 @@
         <v>26</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -1164,14 +1159,14 @@
         <v>26</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33" s="9"/>
     </row>
@@ -1180,14 +1175,14 @@
         <v>26</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F34" s="9"/>
     </row>
@@ -1196,14 +1191,14 @@
         <v>26</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="9" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F35" s="9"/>
     </row>
@@ -1212,7 +1207,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>20</v>
@@ -1221,7 +1216,7 @@
         <v>31</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F36" s="9"/>
     </row>
@@ -1230,7 +1225,7 @@
         <v>26</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>20</v>
@@ -1239,7 +1234,7 @@
         <v>31</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>33</v>
@@ -1250,7 +1245,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>20</v>
@@ -1259,7 +1254,7 @@
         <v>31</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F38" s="9"/>
     </row>
@@ -1268,7 +1263,7 @@
         <v>26</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>20</v>
@@ -1277,25 +1272,23 @@
         <v>31</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>31</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D40" s="8"/>
       <c r="E40" s="9" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F40" s="9"/>
     </row>
@@ -1304,14 +1297,14 @@
         <v>34</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F41" s="9"/>
     </row>
@@ -1320,7 +1313,7 @@
         <v>34</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>35</v>
@@ -1336,14 +1329,14 @@
         <v>34</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="9" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F43" s="9"/>
     </row>
@@ -1352,30 +1345,22 @@
         <v>34</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="9" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="9" t="s">
-        <v>75</v>
-      </c>
+      <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBF05473-2F83-4388-8A24-8CFF0CEF224B}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{8C5950D7-46E5-4BEE-BF2B-CB3E59241E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABFAE745-AFC8-4474-9ABE-2C15AC7B556F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="77">
   <si>
     <t>Menú de Santa Ana 109 — Golconda</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Sopa de ajiaco</t>
   </si>
   <si>
-    <t>Elige tu proteína</t>
-  </si>
-  <si>
     <t>Domingo</t>
   </si>
   <si>
@@ -139,118 +136,127 @@
     <t>Carne de res / pollo / chuleta de cerdo</t>
   </si>
   <si>
-    <t>Ensalada romana</t>
-  </si>
-  <si>
-    <t>19 oct</t>
-  </si>
-  <si>
-    <t>Sopa de sancocho</t>
-  </si>
-  <si>
-    <t>Goulash</t>
-  </si>
-  <si>
-    <t>Puré de papa</t>
-  </si>
-  <si>
-    <t>Habichuelas rancheras</t>
-  </si>
-  <si>
-    <t>20 oct</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de maíz</t>
-  </si>
-  <si>
-    <t>Pollo a la jardinera</t>
-  </si>
-  <si>
-    <t>Torta de mazorca</t>
-  </si>
-  <si>
-    <t>21 oct</t>
-  </si>
-  <si>
     <t>Opción 1</t>
   </si>
   <si>
-    <t>Mondongo</t>
-  </si>
-  <si>
-    <t>Patacón</t>
-  </si>
-  <si>
-    <t>Sopa de durena</t>
-  </si>
-  <si>
-    <t>Carne de res / Chuleta de cerdo / Pollo a la plancha</t>
-  </si>
-  <si>
-    <t>Sidra en salsa al pimentón</t>
-  </si>
-  <si>
-    <t>22 oct</t>
-  </si>
-  <si>
-    <t>Sopa de verduras</t>
-  </si>
-  <si>
-    <t>Pollo a la americana</t>
-  </si>
-  <si>
-    <t>Cascos de papa</t>
-  </si>
-  <si>
-    <t>Ensalada florentina</t>
-  </si>
-  <si>
-    <t>Arroz a las finas hierbas</t>
-  </si>
-  <si>
-    <t>23 oct</t>
-  </si>
-  <si>
-    <t>Sopa de torrejas</t>
-  </si>
-  <si>
-    <t>Pulpa de cerdo a la plancha</t>
-  </si>
-  <si>
-    <t>Papa criolla dorada</t>
-  </si>
-  <si>
-    <t>Pepinos rellenos con verduras</t>
-  </si>
-  <si>
-    <t>24 oct</t>
-  </si>
-  <si>
-    <t>Papa en chupe</t>
-  </si>
-  <si>
-    <t>Ensalada veraniega</t>
-  </si>
-  <si>
-    <t>25 oct</t>
-  </si>
-  <si>
-    <t>Crema de palmitos de cangrejo</t>
-  </si>
-  <si>
-    <t>Trucha al ajillo</t>
-  </si>
-  <si>
-    <t>Arroz con coco</t>
-  </si>
-  <si>
-    <t>Arroz Blanco</t>
-  </si>
-  <si>
-    <t>Platano chip</t>
-  </si>
-  <si>
-    <t>Ensalada arcoíris</t>
+    <t>26 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cebada perlada</t>
+  </si>
+  <si>
+    <t>Carne al vino</t>
+  </si>
+  <si>
+    <t>Croquetas de papa</t>
+  </si>
+  <si>
+    <t>Ensalada waldorf</t>
+  </si>
+  <si>
+    <t>Arroz al perejíl</t>
+  </si>
+  <si>
+    <t>27 oct</t>
+  </si>
+  <si>
+    <t>Sopa de macarrones</t>
+  </si>
+  <si>
+    <t>Pollo mediterráneo</t>
+  </si>
+  <si>
+    <t>Papa a la griega</t>
+  </si>
+  <si>
+    <t>Ensalada césar</t>
+  </si>
+  <si>
+    <t>Arroz con quinoa</t>
+  </si>
+  <si>
+    <t>28 oct</t>
+  </si>
+  <si>
+    <t>Crema de tomate</t>
+  </si>
+  <si>
+    <t>Tacos de carne desmechada</t>
+  </si>
+  <si>
+    <t>Fríjoles</t>
+  </si>
+  <si>
+    <t>Guacamole</t>
+  </si>
+  <si>
+    <t>Ensalada pico e gallo</t>
+  </si>
+  <si>
+    <t>Arroz amarillo</t>
+  </si>
+  <si>
+    <t>29 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cascabeles</t>
+  </si>
+  <si>
+    <t>Soufflé de pollo y atún</t>
+  </si>
+  <si>
+    <t>Papa chip</t>
+  </si>
+  <si>
+    <t>Ensalada de huevo moscovita</t>
+  </si>
+  <si>
+    <t>30 oct</t>
+  </si>
+  <si>
+    <t>Sopa de tortilla de huevo</t>
+  </si>
+  <si>
+    <t>Mojarra frita</t>
+  </si>
+  <si>
+    <t>Ensalada rusa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lechuga, tomate, aguacate y pepino cohombro </t>
+  </si>
+  <si>
+    <t>A la vinagreta</t>
+  </si>
+  <si>
+    <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>31 oct</t>
+  </si>
+  <si>
+    <t>Escoge tu proteína</t>
+  </si>
+  <si>
+    <t>Ensalada oriental</t>
+  </si>
+  <si>
+    <t>1 nov</t>
+  </si>
+  <si>
+    <t>Sopa de pasta</t>
+  </si>
+  <si>
+    <t>Pollo tropical</t>
+  </si>
+  <si>
+    <t>Dedito de queso mozarella</t>
+  </si>
+  <si>
+    <t>Verduras al gratín</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
   </si>
 </sst>
 </file>
@@ -356,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -385,6 +391,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,15 +649,15 @@
       <c r="A2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>38</v>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -656,15 +665,15 @@
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>38</v>
+      <c r="B3" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="9"/>
     </row>
@@ -672,15 +681,15 @@
       <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>38</v>
+      <c r="B4" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -688,15 +697,15 @@
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>38</v>
+      <c r="B5" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="9"/>
     </row>
@@ -704,15 +713,15 @@
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>38</v>
+      <c r="B6" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="F6" s="9"/>
     </row>
@@ -720,7 +729,7 @@
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -736,7 +745,7 @@
       <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -752,7 +761,7 @@
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -768,7 +777,7 @@
       <c r="A10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -776,7 +785,7 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F10" s="9"/>
     </row>
@@ -784,7 +793,7 @@
       <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -792,7 +801,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -800,17 +809,15 @@
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>47</v>
+      <c r="B12" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="D12" s="8"/>
       <c r="E12" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -818,17 +825,15 @@
       <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>47</v>
+      <c r="B13" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="D13" s="8"/>
       <c r="E13" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -836,17 +841,15 @@
       <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>47</v>
+      <c r="B14" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="D14" s="8"/>
       <c r="E14" s="9" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -854,17 +857,15 @@
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>47</v>
+      <c r="B15" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>48</v>
-      </c>
+      <c r="D15" s="8"/>
       <c r="E15" s="9" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -872,17 +873,15 @@
       <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>47</v>
+      <c r="B16" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D16" s="8"/>
       <c r="E16" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -890,73 +889,63 @@
       <c r="A17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>47</v>
+      <c r="B17" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D17" s="8"/>
       <c r="E17" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D18" s="8"/>
       <c r="E18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>33</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D19" s="8"/>
       <c r="E19" s="9" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>31</v>
-      </c>
+      <c r="D20" s="8"/>
       <c r="E20" s="9" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -964,15 +953,15 @@
       <c r="A21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>54</v>
+      <c r="B21" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F21" s="9"/>
     </row>
@@ -980,63 +969,63 @@
       <c r="A22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>54</v>
+      <c r="B22" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="9" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F25" s="9"/>
     </row>
@@ -1044,79 +1033,88 @@
       <c r="A26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>60</v>
+      <c r="B26" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="9"/>
+        <v>65</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>60</v>
+      <c r="B27" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="8"/>
+      <c r="D28" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="E28" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="E29" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" s="9"/>
+        <v>29</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="E30" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F30" s="9"/>
     </row>
@@ -1124,15 +1122,17 @@
       <c r="A31" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>65</v>
+      <c r="B31" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="8"/>
+      <c r="D31" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="E31" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F31" s="9"/>
     </row>
@@ -1140,49 +1140,55 @@
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>65</v>
+      <c r="B32" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="8"/>
+      <c r="D32" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="E32" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>28</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>65</v>
+      <c r="B33" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="E33" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="9"/>
+        <v>35</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>65</v>
+      <c r="B34" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="8"/>
+      <c r="D34" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="E34" s="9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F34" s="9"/>
     </row>
@@ -1190,15 +1196,17 @@
       <c r="A35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>65</v>
+      <c r="B35" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="8"/>
+      <c r="D35" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="E35" s="9" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F35" s="9"/>
     </row>
@@ -1206,8 +1214,8 @@
       <c r="A36" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>65</v>
+      <c r="B36" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>20</v>
@@ -1216,144 +1224,111 @@
         <v>31</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F36" s="9"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>65</v>
+        <v>33</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D37" s="8"/>
       <c r="E37" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>33</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F37" s="9"/>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>65</v>
+        <v>33</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D38" s="8"/>
       <c r="E38" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>65</v>
+        <v>33</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D39" s="8"/>
       <c r="E39" s="9" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F41" s="9"/>
+        <v>76</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A42" s="7"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="9" t="s">
-        <v>73</v>
-      </c>
+      <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A44" s="7"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="9" t="s">
-        <v>71</v>
-      </c>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
